--- a/artfynd/A 44308-2021 artfynd.xlsx
+++ b/artfynd/A 44308-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 44308-2021 artfynd.xlsx
+++ b/artfynd/A 44308-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>62265636</v>
+        <v>62265616</v>
       </c>
       <c r="B2" t="n">
-        <v>90319</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87309</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,26 +686,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4769</v>
+        <v>3674</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -724,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>694712.2349813199</v>
+        <v>694743</v>
       </c>
       <c r="R2" t="n">
-        <v>6384262.002439265</v>
+        <v>6384378</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -757,19 +752,9 @@
           <t>2016-09-21</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2016-10-24</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -793,6 +778,950 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>62265630</v>
+      </c>
+      <c r="B3" t="n">
+        <v>87146</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>3762</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Olivspindling</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Cortinarius venetus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Stenkumla Kviungs 1:25, Gtl</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>694742</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6384341</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Stenkumla</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2016-09-21</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2016-10-24</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Åke Edvinsson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Åke Edvinsson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>62265635</v>
+      </c>
+      <c r="B4" t="n">
+        <v>92869</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>4769</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Svavelriska</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Stenkumla Kviungs 1:25, Gtl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>694712</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6384234</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Stenkumla</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2016-09-21</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2016-10-24</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Åke Edvinsson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Åke Edvinsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>62265636</v>
+      </c>
+      <c r="B5" t="n">
+        <v>92869</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>4769</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Svavelriska</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Stenkumla Kviungs 1:25, Gtl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>694712</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6384262</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Stenkumla</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2016-09-21</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2016-10-24</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Åke Edvinsson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Åke Edvinsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>62265637</v>
+      </c>
+      <c r="B6" t="n">
+        <v>92869</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>4769</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Svavelriska</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Stenkumla Kviungs 1:25, Gtl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>694743</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6384378</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Stenkumla</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2016-09-21</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2016-10-24</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Åke Edvinsson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Åke Edvinsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>118765237</v>
+      </c>
+      <c r="B7" t="n">
+        <v>111390</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>219711</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Sårläka</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Sanicula europaea</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Stenkumla, Gtl</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>694742</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6384297</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Stenkumla</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-06-13</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-06-13</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Tony Svensson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Tony Svensson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>118765619</v>
+      </c>
+      <c r="B8" t="n">
+        <v>110078</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Stenkumla, Gtl</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>694510</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6384704</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Stenkumla</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-06-13</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-06-13</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Tony Svensson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Johan Engström</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>62265661</v>
+      </c>
+      <c r="B9" t="n">
+        <v>92688</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>232138</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Gul lammticka</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Albatrellus citrinus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Ryman</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Stenkumla Kviungs 1:25, Gtl</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>694746</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6384431</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Stenkumla</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2016-09-21</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2016-10-24</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Åke Edvinsson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Åke Edvinsson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>62265646</v>
+      </c>
+      <c r="B10" t="n">
+        <v>87291</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>248955</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tvillingspindling</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Cortinarius metarius</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Kauffman</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Stenkumla Kviungs 1:25, Gtl</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>694735</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6384344</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Stenkumla</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2016-09-21</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2016-10-24</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Åke Edvinsson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Åke Edvinsson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>62331163</v>
+      </c>
+      <c r="B11" t="n">
+        <v>87323</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>249228</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Barrfagerspindling</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Cortinarius piceae</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Frøslev &amp; al.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Stenkumla Kviungs 1:25, Gtl</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>694742</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6384341</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Stenkumla</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2016-09-25</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2016-10-24</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Åke Edvinsson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Åke Edvinsson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 44308-2021 artfynd.xlsx
+++ b/artfynd/A 44308-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62265616</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62265630</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -990,6 +1005,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62265635</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1096,6 +1116,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62265636</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1202,6 +1227,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62265637</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1303,6 +1333,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118765237</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1404,6 +1439,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118765619</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1510,6 +1550,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62265661</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1616,6 +1661,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62265646</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1722,8 +1772,25 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62331163</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>